--- a/htr-corps-ressources-FHIR/ig/StructureDefinition-fr-observation-synthese-medicale-sejour-document.xlsx
+++ b/htr-corps-ressources-FHIR/ig/StructureDefinition-fr-observation-synthese-medicale-sejour-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$88</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2414" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3388" uniqueCount="591">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-01T13:19:09+00:00</t>
+    <t>2025-09-02T15:19:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1082,6 +1082,245 @@
     <t>FiveWs.actor</t>
   </si>
   <si>
+    <t>Observation.performer.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author</t>
+  </si>
+  <si>
+    <t>author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension}
+</t>
+  </si>
+  <si>
+    <t>Extension pour représenter un acteur impliqué dans le document avec son type et sa référence.</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.extension</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:type</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:type.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.extension.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:type.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:type.url</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>AUT</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-actor-type</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:typeCode</t>
+  </si>
+  <si>
+    <t>typeCode</t>
+  </si>
+  <si>
+    <t>Type de participation</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:typeCode.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:typeCode.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:typeCode.url</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:typeCode.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:reference</t>
+  </si>
+  <si>
+    <t>reference</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:reference.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:reference.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:reference.url</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:reference.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-organization-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document)
+</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.url</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.url</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.value[x]</t>
+  </si>
+  <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+  </si>
+  <si>
+    <t>Observation.performer.reference</t>
+  </si>
+  <si>
+    <t>Literal reference, Relative, internal or absolute URL</t>
+  </si>
+  <si>
+    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
+  </si>
+  <si>
+    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
+  </si>
+  <si>
+    <t>Reference.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref-1
+</t>
+  </si>
+  <si>
+    <t>Observation.performer.type</t>
+  </si>
+  <si>
+    <t>Type the reference refers to (e.g. "Patient")</t>
+  </si>
+  <si>
+    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
+The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
+  </si>
+  <si>
+    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+  </si>
+  <si>
+    <t>Reference.type</t>
+  </si>
+  <si>
+    <t>Observation.performer.identifier</t>
+  </si>
+  <si>
+    <t>Logical reference, when literal reference is not known</t>
+  </si>
+  <si>
+    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
+  </si>
+  <si>
+    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
+When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
+Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
+Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
+  </si>
+  <si>
+    <t>Reference.identifier</t>
+  </si>
+  <si>
+    <t>.identifier</t>
+  </si>
+  <si>
+    <t>Observation.performer.display</t>
+  </si>
+  <si>
+    <t>Text alternative for the resource</t>
+  </si>
+  <si>
+    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
+  </si>
+  <si>
+    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>Reference.display</t>
+  </si>
+  <si>
     <t>Observation.value[x]</t>
   </si>
   <si>
@@ -1127,9 +1366,6 @@
   </si>
   <si>
     <t>For many results it is necessary to handle exceptional values in measurements.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
@@ -1938,11 +2174,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP62"/>
+  <dimension ref="A1:AP88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="38.30078125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="57.26171875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="43.44921875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -5981,35 +6217,31 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>217</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>344</v>
+        <v>218</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -6057,7 +6289,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>343</v>
+        <v>220</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6066,47 +6298,47 @@
         <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>351</v>
+        <v>221</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>352</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -6118,20 +6350,18 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>192</v>
+        <v>139</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>354</v>
+        <v>140</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>355</v>
+        <v>223</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -6155,43 +6385,43 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>358</v>
+        <v>82</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>360</v>
+        <v>82</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>353</v>
+        <v>227</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>361</v>
+        <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
@@ -6200,10 +6430,10 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>362</v>
+        <v>221</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6214,14 +6444,16 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>346</v>
+      </c>
       <c r="D36" t="s" s="2">
-        <v>364</v>
+        <v>82</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6231,7 +6463,7 @@
         <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>82</v>
@@ -6240,20 +6472,16 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>192</v>
+        <v>347</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>365</v>
+        <v>336</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>368</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6277,11 +6505,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y36" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z36" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6299,7 +6529,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>363</v>
+        <v>227</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6311,33 +6541,33 @@
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>371</v>
+        <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>372</v>
+        <v>82</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>373</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>374</v>
+        <v>349</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>374</v>
+        <v>350</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6348,10 +6578,10 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>82</v>
@@ -6360,20 +6590,16 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>375</v>
+        <v>217</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>376</v>
+        <v>218</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6421,19 +6647,19 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>374</v>
+        <v>220</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
@@ -6442,10 +6668,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>380</v>
+        <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>381</v>
+        <v>221</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6456,10 +6682,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>382</v>
+        <v>351</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>382</v>
+        <v>352</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6467,10 +6693,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>353</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6482,17 +6708,15 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>192</v>
+        <v>139</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>383</v>
+        <v>354</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>385</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6517,83 +6741,85 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>386</v>
+        <v>82</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>382</v>
+        <v>227</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>388</v>
+        <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>389</v>
+        <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>390</v>
+        <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>391</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>392</v>
+        <v>356</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="C39" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="D39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
@@ -6602,20 +6828,16 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>192</v>
+        <v>139</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>393</v>
+        <v>354</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>396</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
@@ -6639,11 +6861,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y39" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>397</v>
+        <v>82</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6661,19 +6885,19 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>392</v>
+        <v>227</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
@@ -6682,10 +6906,10 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>398</v>
+        <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>399</v>
+        <v>82</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6696,10 +6920,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>400</v>
+        <v>358</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>400</v>
+        <v>359</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6722,17 +6946,15 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>401</v>
+        <v>217</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>402</v>
+        <v>218</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>404</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6781,7 +7003,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>400</v>
+        <v>220</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6793,33 +7015,33 @@
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>405</v>
+        <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>406</v>
+        <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>407</v>
+        <v>221</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>408</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>409</v>
+        <v>360</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>409</v>
+        <v>361</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6830,7 +7052,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -6842,17 +7064,15 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>410</v>
+        <v>139</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>411</v>
+        <v>354</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -6889,57 +7109,57 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>409</v>
+        <v>227</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>414</v>
+        <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>415</v>
+        <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>416</v>
+        <v>82</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>417</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>418</v>
+        <v>362</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>418</v>
+        <v>363</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6947,10 +7167,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -6962,26 +7182,24 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>419</v>
+        <v>107</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>420</v>
+        <v>364</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>421</v>
+        <v>365</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>423</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>82</v>
+        <v>357</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>82</v>
@@ -7023,19 +7241,19 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>418</v>
+        <v>367</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>424</v>
+        <v>82</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -7044,10 +7262,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>425</v>
+        <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>426</v>
+        <v>136</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7058,10 +7276,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>427</v>
+        <v>368</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>427</v>
+        <v>369</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7084,13 +7302,13 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>217</v>
+        <v>113</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>218</v>
+        <v>370</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>219</v>
+        <v>371</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7099,7 +7317,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>82</v>
+        <v>372</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>82</v>
@@ -7117,13 +7335,11 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>82</v>
+        <v>373</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7141,7 +7357,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>220</v>
+        <v>374</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7153,7 +7369,7 @@
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
@@ -7165,7 +7381,7 @@
         <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>221</v>
+        <v>136</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7176,21 +7392,23 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>428</v>
+        <v>375</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="D44" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -7205,14 +7423,12 @@
         <v>139</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>140</v>
+        <v>377</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7285,7 +7501,7 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>221</v>
+        <v>82</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7296,46 +7512,42 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>429</v>
+        <v>378</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>429</v>
+        <v>359</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>430</v>
+        <v>82</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>139</v>
+        <v>217</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>431</v>
+        <v>218</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7383,19 +7595,19 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>433</v>
+        <v>220</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7407,7 +7619,7 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>136</v>
+        <v>221</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7418,10 +7630,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>434</v>
+        <v>379</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>434</v>
+        <v>361</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7432,7 +7644,7 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7444,13 +7656,13 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>435</v>
+        <v>139</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>436</v>
+        <v>354</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>437</v>
+        <v>355</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7489,31 +7701,31 @@
         <v>82</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>434</v>
+        <v>227</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>438</v>
+        <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7522,10 +7734,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>439</v>
+        <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>440</v>
+        <v>82</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7536,10 +7748,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>441</v>
+        <v>380</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>441</v>
+        <v>363</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7547,7 +7759,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>93</v>
@@ -7562,22 +7774,24 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>435</v>
+        <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>442</v>
+        <v>364</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>82</v>
+        <v>376</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>82</v>
@@ -7619,19 +7833,19 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>441</v>
+        <v>367</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>438</v>
+        <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -7640,10 +7854,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>439</v>
+        <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>444</v>
+        <v>136</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7654,10 +7868,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>445</v>
+        <v>381</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>445</v>
+        <v>369</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7683,17 +7897,13 @@
         <v>192</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>446</v>
+        <v>370</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>449</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -7717,13 +7927,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>450</v>
+        <v>82</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>451</v>
+        <v>82</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7741,7 +7951,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>445</v>
+        <v>374</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7759,13 +7969,13 @@
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>452</v>
+        <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>453</v>
+        <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>372</v>
+        <v>136</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7776,21 +7986,23 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>454</v>
+        <v>382</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="C49" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="D49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -7802,20 +8014,16 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>192</v>
+        <v>139</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>455</v>
+        <v>354</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>458</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
@@ -7839,13 +8047,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>459</v>
+        <v>82</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>460</v>
+        <v>82</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -7863,7 +8071,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>454</v>
+        <v>227</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7875,19 +8083,19 @@
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>452</v>
+        <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>453</v>
+        <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>372</v>
+        <v>82</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -7898,10 +8106,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>461</v>
+        <v>384</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>461</v>
+        <v>359</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7924,18 +8132,16 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>462</v>
+        <v>217</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>463</v>
+        <v>218</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>464</v>
+        <v>219</v>
       </c>
       <c r="N50" s="2"/>
-      <c r="O50" t="s" s="2">
-        <v>465</v>
-      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
@@ -7983,7 +8189,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>461</v>
+        <v>220</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7995,7 +8201,7 @@
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
@@ -8007,7 +8213,7 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>466</v>
+        <v>221</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8018,10 +8224,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>467</v>
+        <v>385</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>467</v>
+        <v>361</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8032,7 +8238,7 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
@@ -8044,13 +8250,13 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>217</v>
+        <v>139</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>468</v>
+        <v>354</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>469</v>
+        <v>355</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8089,31 +8295,31 @@
         <v>82</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>467</v>
+        <v>227</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
@@ -8122,10 +8328,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>439</v>
+        <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>470</v>
+        <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8136,10 +8342,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>471</v>
+        <v>386</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>471</v>
+        <v>363</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8147,10 +8353,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8159,19 +8365,19 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>472</v>
+        <v>107</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>473</v>
+        <v>364</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>474</v>
+        <v>365</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>475</v>
+        <v>366</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8179,7 +8385,7 @@
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>82</v>
+        <v>383</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>82</v>
@@ -8221,19 +8427,19 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>471</v>
+        <v>367</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8242,10 +8448,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>476</v>
+        <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>477</v>
+        <v>136</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8256,10 +8462,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>478</v>
+        <v>387</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>478</v>
+        <v>369</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8270,7 +8476,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>82</v>
@@ -8279,20 +8485,18 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>479</v>
+        <v>388</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>480</v>
+        <v>370</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>482</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8341,13 +8545,13 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>478</v>
+        <v>374</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
@@ -8362,10 +8566,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>476</v>
+        <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>483</v>
+        <v>136</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8376,10 +8580,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>484</v>
+        <v>389</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>484</v>
+        <v>390</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8387,10 +8591,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8399,29 +8603,27 @@
         <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>419</v>
+        <v>107</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>485</v>
+        <v>364</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>486</v>
+        <v>365</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>488</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>82</v>
+        <v>391</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>82</v>
@@ -8463,19 +8665,19 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>484</v>
+        <v>367</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
@@ -8484,10 +8686,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>489</v>
+        <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>490</v>
+        <v>136</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8498,10 +8700,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>491</v>
+        <v>392</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>491</v>
+        <v>393</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8512,7 +8714,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8524,13 +8726,13 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>217</v>
+        <v>394</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>218</v>
+        <v>370</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>219</v>
+        <v>371</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8581,7 +8783,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>220</v>
+        <v>374</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8593,7 +8795,7 @@
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
@@ -8605,7 +8807,7 @@
         <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>221</v>
+        <v>136</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8616,21 +8818,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>492</v>
+        <v>395</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>492</v>
+        <v>395</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>82</v>
@@ -8639,19 +8841,19 @@
         <v>82</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>139</v>
+        <v>217</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>140</v>
+        <v>396</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>223</v>
+        <v>397</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>142</v>
+        <v>398</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8701,19 +8903,19 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>227</v>
+        <v>399</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>82</v>
+        <v>400</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
@@ -8725,7 +8927,7 @@
         <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>221</v>
+        <v>136</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8736,46 +8938,44 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>493</v>
+        <v>401</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>493</v>
+        <v>401</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>430</v>
+        <v>82</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>431</v>
+        <v>402</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>432</v>
+        <v>403</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -8799,13 +8999,13 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>82</v>
+        <v>406</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>82</v>
+        <v>407</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -8823,19 +9023,19 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>433</v>
+        <v>408</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
@@ -8858,10 +9058,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>494</v>
+        <v>409</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>494</v>
+        <v>409</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8869,7 +9069,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>93</v>
@@ -8884,20 +9084,18 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>192</v>
+        <v>151</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>495</v>
+        <v>410</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>496</v>
+        <v>411</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
       </c>
@@ -8921,13 +9119,13 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>209</v>
+        <v>82</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -8945,10 +9143,10 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>494</v>
+        <v>413</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>93</v>
@@ -8963,16 +9161,16 @@
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>498</v>
+        <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>212</v>
+        <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>213</v>
+        <v>414</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>214</v>
+        <v>82</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -8980,10 +9178,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>499</v>
+        <v>415</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>499</v>
+        <v>415</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9006,20 +9204,18 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>500</v>
+        <v>217</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>501</v>
+        <v>416</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>345</v>
+        <v>417</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9067,7 +9263,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>499</v>
+        <v>419</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9085,27 +9281,27 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>503</v>
+        <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>351</v>
+        <v>136</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>352</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>504</v>
+        <v>420</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>504</v>
+        <v>420</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9113,34 +9309,34 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>505</v>
+        <v>421</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>506</v>
+        <v>422</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>507</v>
+        <v>423</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>357</v>
+        <v>424</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9165,13 +9361,13 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>358</v>
+        <v>82</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>360</v>
+        <v>82</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9189,7 +9385,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>504</v>
+        <v>420</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9198,7 +9394,7 @@
         <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>361</v>
+        <v>425</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>105</v>
@@ -9207,38 +9403,38 @@
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>82</v>
+        <v>426</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>136</v>
+        <v>427</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>362</v>
+        <v>428</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>508</v>
+        <v>430</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>508</v>
+        <v>430</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>364</v>
+        <v>82</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -9253,16 +9449,16 @@
         <v>192</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>509</v>
+        <v>431</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>366</v>
+        <v>432</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>367</v>
+        <v>433</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>368</v>
+        <v>434</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9287,13 +9483,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>358</v>
+        <v>405</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>510</v>
+        <v>435</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>511</v>
+        <v>436</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9311,16 +9507,16 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>508</v>
+        <v>430</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>82</v>
+        <v>437</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>105</v>
@@ -9329,41 +9525,41 @@
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>371</v>
+        <v>136</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>372</v>
+        <v>438</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>373</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>512</v>
+        <v>439</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>512</v>
+        <v>439</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>82</v>
@@ -9372,19 +9568,19 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>83</v>
+        <v>192</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>513</v>
+        <v>441</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>514</v>
+        <v>442</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9409,13 +9605,11 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9433,7 +9627,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>512</v>
+        <v>439</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9451,23 +9645,3157 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>82</v>
+        <v>446</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>425</v>
+        <v>447</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>426</v>
+        <v>448</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP62" t="s" s="2">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="Y65" s="2"/>
+      <c r="Z65" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP76" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP77" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP78" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP79" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="P80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP80" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AO81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP81" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP82" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="P83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AO83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP83" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="P84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AP84" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="P85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP85" t="s" s="2">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="P86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP86" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="P87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP87" t="s" s="2">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="P88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AO88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP88" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP62">
+  <autoFilter ref="A1:AP88">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9477,7 +12805,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI61">
+  <conditionalFormatting sqref="A2:AI87">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
